--- a/backend/src/db/demo-docs/measurements-core-crew-sweatshirt.xlsx
+++ b/backend/src/db/demo-docs/measurements-core-crew-sweatshirt.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Poly Spandex Blend</t>
+          <t>88% Polyester 12% Spandex</t>
         </is>
       </c>
     </row>
@@ -589,19 +589,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
+        <v>53</v>
+      </c>
+      <c r="E10" s="5" t="n">
         <v>56</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="F10" s="5" t="n">
         <v>59</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="G10" s="5" t="n">
         <v>62</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="H10" s="5" t="n">
         <v>65.5</v>
       </c>
     </row>
@@ -682,19 +685,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D13" s="5" t="n">
+        <v>71.5</v>
+      </c>
+      <c r="E13" s="5" t="n">
         <v>73.5</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="F13" s="5" t="n">
         <v>75.5</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="G13" s="5" t="n">
         <v>77.5</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="H13" s="5" t="n">
         <v>79.5</v>
       </c>
     </row>
@@ -711,19 +717,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D14" s="5" t="n">
+        <v>49</v>
+      </c>
+      <c r="E14" s="5" t="n">
         <v>50.5</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="F14" s="5" t="n">
         <v>52</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="G14" s="5" t="n">
         <v>53.5</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="H14" s="5" t="n">
         <v>55</v>
       </c>
     </row>
@@ -772,19 +781,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D16" s="5" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="E16" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="F16" s="5" t="n">
         <v>21.5</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="G16" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="H16" s="5" t="n">
         <v>22.5</v>
       </c>
     </row>
@@ -801,19 +813,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D17" s="5" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="E17" s="5" t="n">
         <v>23.5</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="F17" s="5" t="n">
         <v>24.5</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="G17" s="5" t="n">
         <v>25.5</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="H17" s="5" t="n">
         <v>26.5</v>
       </c>
     </row>
@@ -830,19 +845,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E18" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="F18" s="5" t="n">
         <v>9.5</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="G18" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="H18" s="5" t="n">
         <v>10.5</v>
       </c>
     </row>
@@ -859,7 +877,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -869,11 +887,14 @@
         <v>2</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="G19" s="5" t="n">
         <v>2.5</v>
       </c>
+      <c r="H19" s="5" t="n">
+        <v>2.5</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -888,19 +909,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="E20" s="5" t="n">
         <v>81.5</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="F20" s="5" t="n">
         <v>83.5</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="G20" s="5" t="n">
         <v>85.5</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="H20" s="5" t="n">
         <v>87.5</v>
       </c>
     </row>
@@ -1013,14 +1037,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
         <v>4.5</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="F24" s="5" t="n">
         <v>5</v>
@@ -1028,6 +1052,9 @@
       <c r="G24" s="5" t="n">
         <v>5</v>
       </c>
+      <c r="H24" s="5" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1042,7 +1069,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>±0.5</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
@@ -1055,6 +1082,9 @@
         <v>2</v>
       </c>
       <c r="G25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="5" t="n">
         <v>2</v>
       </c>
     </row>
